--- a/reports/一级子公司B_现金流量表_2026-03.xlsx
+++ b/reports/一级子公司B_现金流量表_2026-03.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>48204000</v>
+        <v>46634639</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>133043040</v>
+        <v>129233746</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1018540</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>2800370</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>504489</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>1396968</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>254745</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>701456</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>201917</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>557944</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>152609</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>421253</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>101199</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>278914</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>76082</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>210520</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>50761</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>139622</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>126410</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>350266</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>63948</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>175787</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>40111</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>111119</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>154500</v>
+        <v>150750</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>426420</v>
+        <v>414826</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>927000</v>
+        <v>895694</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>2558520</v>
+        <v>2477037</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>49285500</v>
+        <v>50271894</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>24720000</v>
+        <v>23959123</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>68227200</v>
+        <v>66367290</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>339053</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>932047</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>252435</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>699499</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>169819</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>467059</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>126118</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>349030</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>84889</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>233921</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>63462</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>175212</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8755000</v>
+        <v>8521138</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>24163800</v>
+        <v>23541227</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3296000</v>
+        <v>3196888</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>9096960</v>
+        <v>8804186</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1854000</v>
+        <v>1798842</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>5117040</v>
+        <v>4980454</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>38625000</v>
+        <v>38511767</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>10660500</v>
+        <v>11760127</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>61800</v>
+        <v>60202</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>185400</v>
+        <v>180626</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>618000</v>
+        <v>600268</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>1854000</v>
+        <v>1805558</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>370800</v>
+        <v>360419</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>1112400</v>
+        <v>1077418</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>679800</v>
+        <v>660470</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6180000</v>
+        <v>6023213</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>18540000</v>
+        <v>17993783</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>927000</v>
+        <v>895790</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>2781000</v>
+        <v>2697870</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4326000</v>
+        <v>4220986</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>12978000</v>
+        <v>12623188</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>144200</v>
+        <v>140212</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>432600</v>
+        <v>421419</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6324200</v>
+        <v>6163425</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5644400</v>
+        <v>-5502955</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1236000</v>
+        <v>1194981</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>3708000</v>
+        <v>3599902</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2060000</v>
+        <v>1990024</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>6180000</v>
+        <v>5987115</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2060000</v>
+        <v>2009232</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>6180000</v>
+        <v>6017538</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>61800</v>
+        <v>59774</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>185400</v>
+        <v>179389</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3357800</v>
+        <v>3244779</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1648000</v>
+        <v>1598395</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>4944000</v>
+        <v>4784368</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>1648000</v>
+        <v>1599020</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>4944000</v>
+        <v>4812789</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>288400</v>
+        <v>280606</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>865200</v>
+        <v>838493</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>247200</v>
+        <v>241068</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>741600</v>
+        <v>720287</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>36050</v>
+        <v>34827</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>108150</v>
+        <v>104844</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>1972450</v>
+        <v>1913828</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1385350</v>
+        <v>1330951</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>6401450</v>
+        <v>7588123</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>6401450</v>
+        <v>7588123</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
